--- a/data/trans_orig/P21D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención dental en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117318</t>
+          <t>116559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146783</t>
+          <t>146089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166808</t>
+          <t>166911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196740</t>
+          <t>196023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292418</t>
+          <t>291852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>334528</t>
+          <t>333944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72581</t>
+          <t>73721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101690</t>
+          <t>103251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119138</t>
+          <t>118460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>147813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201554</t>
+          <t>202691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242610</t>
+          <t>242738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48478</t>
+          <t>44154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>187226</t>
+          <t>179202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>464346</t>
+          <t>467064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>332502</t>
+          <t>333478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>496106</t>
+          <t>520473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>509551</t>
+          <t>499939</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>879803</t>
+          <t>873502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619371</t>
+          <t>618197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>917169</t>
+          <t>926963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>415835</t>
+          <t>394171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>573353</t>
+          <t>570752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1120077</t>
+          <t>1117790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1499380</t>
+          <t>1517011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41031</t>
+          <t>43288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>48305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83159</t>
+          <t>81850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116074</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>91301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154912</t>
+          <t>153046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198652</t>
+          <t>199176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>192156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225793</t>
+          <t>226162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213104</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>242554</t>
+          <t>242163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>414385</t>
+          <t>413358</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>458957</t>
+          <t>460650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>346188</t>
+          <t>365868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>700056</t>
+          <t>699574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>590543</t>
+          <t>590008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>776431</t>
+          <t>774933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>956671</t>
+          <t>912272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1375490</t>
+          <t>1365994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>912284</t>
+          <t>912569</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1292144</t>
+          <t>1271159</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>751610</t>
+          <t>748134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>936267</t>
+          <t>935937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1770102</t>
+          <t>1774200</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2214773</t>
+          <t>2255471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>37830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>57131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84447</t>
+          <t>82590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>131830</t>
+          <t>147938</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116559</t>
+          <t>131269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146089</t>
+          <t>163093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>182122</t>
+          <t>203055</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>186263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196023</t>
+          <t>217355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>313952</t>
+          <t>350993</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291852</t>
+          <t>328665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>333944</t>
+          <t>371762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87697</t>
+          <t>90890</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73721</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103251</t>
+          <t>106662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134220</t>
+          <t>142875</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118460</t>
+          <t>128249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147813</t>
+          <t>157910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>221917</t>
+          <t>233765</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202691</t>
+          <t>212732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242738</t>
+          <t>254487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1064,67 +1064,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12450</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8103</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19731</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16283</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9278</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36253</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>32719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568652</t>
+          <t>617371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>353215</t>
+          <t>410363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179202</t>
+          <t>374543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>467064</t>
+          <t>447063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>386345</t>
+          <t>368920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>333478</t>
+          <t>338163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>520473</t>
+          <t>396570</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>739560</t>
+          <t>779283</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>499939</t>
+          <t>734323</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>873502</t>
+          <t>829413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>738655</t>
+          <t>516590</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>618197</t>
+          <t>480367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>926963</t>
+          <t>552724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>520847</t>
+          <t>580087</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>394171</t>
+          <t>552016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>570752</t>
+          <t>609177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1259502</t>
+          <t>1096677</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1117790</t>
+          <t>1047961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1517011</t>
+          <t>1140407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43288</t>
+          <t>34688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>18333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48305</t>
+          <t>64311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98194</t>
+          <t>111800</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81850</t>
+          <t>93167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115610</t>
+          <t>131539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76843</t>
+          <t>84257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91301</t>
+          <t>100668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>175036</t>
+          <t>196057</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153046</t>
+          <t>171912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>199176</t>
+          <t>223177</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209762</t>
+          <t>233123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192156</t>
+          <t>213909</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>226162</t>
+          <t>251510</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228597</t>
+          <t>250477</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213625</t>
+          <t>234295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>242163</t>
+          <t>265361</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>438359</t>
+          <t>483600</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>413358</t>
+          <t>455938</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>460650</t>
+          <t>508376</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>310628</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>687775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>583238</t>
+          <t>670101</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>365868</t>
+          <t>628513</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>699574</t>
+          <t>717183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>645310</t>
+          <t>656232</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>590008</t>
+          <t>619919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>774933</t>
+          <t>692379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1228548</t>
+          <t>1326333</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>912272</t>
+          <t>1265007</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1365994</t>
+          <t>1380987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1036114</t>
+          <t>840603</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>912569</t>
+          <t>793435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1271159</t>
+          <t>883373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>883664</t>
+          <t>973438</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>748134</t>
+          <t>935841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>935937</t>
+          <t>1009406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1919778</t>
+          <t>1814041</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1774200</t>
+          <t>1755511</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2255471</t>
+          <t>1871849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>57,59%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,67 +2693,67 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>12798</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>35704</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>24301</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>53322</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>33662</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>21418</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>56868</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2771,102 +2771,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37830</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>40555</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>30086</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>53385</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>74096</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>58182</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>92224</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>36433</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>25580</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>61921</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>45160</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>82590</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1585716</t>
+          <t>1689800</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3243909</t>
+          <t>3250174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
